--- a/leads.xlsx
+++ b/leads.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H609"/>
+  <dimension ref="A1:J609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -467,11 +467,16 @@
           <t>Date Added</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Emailed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Diamond Dental – Dental Hospital and Clinic Tirana Albania</t>
+          <t>Diamond Dental</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>info@diamond-dental.al</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -492,13 +502,18 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Contact - Brianza Dent Dental Clinic</t>
+          <t>Brianza Dent Dental Clinic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,6 +526,11 @@
           <t>+355682032462</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>info@brianzadent.al</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -524,13 +544,18 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Best Dental Clinic Tirana | Dental Tourism &amp; Implants</t>
+          <t>Best Dental Clinic Tirana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -589,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dentist In Albania, Tirana | Trio Dental Center 2026</t>
+          <t>Trio Dental Center</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,13 +645,18 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Contact Us En - Poliklinika dentare UFO</t>
+          <t>Poliklinika dentare UFO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,6 +669,11 @@
           <t>+355696047474</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>info@ufodentalclinic.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -652,13 +687,18 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tirana Dental Center – Dental Implants &amp; Surgery in Tirana</t>
+          <t>Tirana Dental Center</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Top 10 Dental Clinics &amp; Dentists in Tirana</t>
+          <t>DentaVacation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,6 +733,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>info@dentavacation.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -706,6 +751,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:30</t>
         </is>
       </c>
     </row>
@@ -752,6 +802,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>info@bookingstomatologist.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -765,6 +820,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:30</t>
         </is>
       </c>
     </row>
@@ -779,6 +839,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiranadentalhospital@gmail.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -792,13 +857,18 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tirana Dental Clinic: Home</t>
+          <t>Tirana Dental Clinic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -830,7 +900,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Klinika Dentare Lako - Studio Dentistico a Tirana Albania ...</t>
+          <t>Klinika Dentare Lako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -838,6 +908,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>info@klinikadentarelako.al</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -851,6 +926,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:30</t>
         </is>
       </c>
     </row>
@@ -865,6 +945,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>info@toti-gurakuqi.al</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -878,6 +963,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
@@ -892,6 +982,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>contact@mjeket.al</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -905,6 +1000,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
@@ -944,11 +1044,16 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:09</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Best Dental Tirana - Light up your life!</t>
+          <t>Best Dental Tirana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -975,7 +1080,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>What Is the Best Dental Clinic in Tirana, Albania?</t>
+          <t>Virtus Dental Center</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -983,6 +1088,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>info@virtus.al</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -996,13 +1106,18 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dental tourism and Dental Care — Dental Med Travel</t>
+          <t>Dental tourism and Dental Care</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1029,7 +1144,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Finesa Dental | Klinika Dentare në Tiranë</t>
+          <t>Finesa Dental</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1037,6 +1152,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>info@finesadental.com</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1050,6 +1170,11 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
@@ -1069,6 +1194,11 @@
           <t>+355692284409</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>info@klinikakristi.al</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1082,13 +1212,18 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>American Dental Hospital | Klinikë Dentare në Tiranë</t>
+          <t>American Dental Hospital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1147,7 +1282,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Implantus - Dental Clinic Specialized in Dental Implants</t>
+          <t>Implantus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1187,6 +1322,11 @@
           <t>+39 02 8718 7132</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>info@dentistiinalbania.com</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1200,13 +1340,18 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cheap Dental Implants: the winning choice in Tirana, Albania</t>
+          <t>Smile Provider</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1214,6 +1359,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>info@smile-provider.com</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1227,13 +1377,18 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Best Dental Implant Clinics in Albania</t>
+          <t>Family Dental Care</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1241,6 +1396,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>info@familydentalcareal.com</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1254,13 +1414,18 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Teeth Whitening in Oxa Clinic in Tirana.</t>
+          <t>Oxa Clinic</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1268,6 +1433,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>info@oxaclinic.com</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1281,6 +1451,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:32</t>
         </is>
       </c>
     </row>
@@ -1295,6 +1470,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>finance@bookimed.com</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1308,13 +1488,18 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Teeth Whitening In Albania: Affordable Prices &amp; Results</t>
+          <t>City Dental Clinic CDC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1322,6 +1507,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>info@cdc.com.al</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1335,6 +1525,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:32</t>
         </is>
       </c>
     </row>
@@ -1349,6 +1544,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>info@whatclinic.com</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1362,13 +1562,18 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dental Clinic Albania | Smile Provider in Tirana</t>
+          <t>Dental Clinic Albania</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1376,6 +1581,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>info@smile-provider.com</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1389,13 +1599,18 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>“Best Dental Tirana” Tirana, Albania @bestdentaltirana ...</t>
+          <t>“Best Dental Tirana” Tirana, Albania @bestdentaltirana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1422,7 +1637,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Endeta Dental Clinic: Top-Rated Dentist in Albania</t>
+          <t>Endeta Dental Clinic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1430,6 +1645,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>info@endetadentalclinic.al</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1443,6 +1663,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
@@ -1457,6 +1682,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>finance@bookimed.com</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1470,13 +1700,18 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kontakt | Finesa Dental | Klinikë Dentare në Tiranë</t>
+          <t>Finesa Dental</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1507,13 +1742,18 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Klinike Dentare "Kertuka Dent" | Tirana</t>
+          <t>Klinike Dentare "Kertuka Dent"</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1553,6 +1793,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>info@toti-gurakuqi.al</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1566,13 +1811,18 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bloom Dental Clinic – Klinikë Dentare në Tiranë</t>
+          <t>Bloom Dental Clinic</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1617,6 +1867,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>info@klinikakristi.al</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1630,13 +1885,18 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:33</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kush Eshte Klinika Dentare Me e Mire ne Tirane?</t>
+          <t>Emerald Dental</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1662,13 +1922,18 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dental Clinic in Tirana - Orthosmile</t>
+          <t>Orthosmile</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1676,6 +1941,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>orthosmiletirana@gmail.com</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1689,13 +1959,18 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Orthodontics In Albania | American Dental Hospital</t>
+          <t>Orthodontics In Albania</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1730,6 +2005,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>info@placidway.com</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1743,13 +2023,18 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dental Clinic in Tirana</t>
+          <t>Orbis Dental Care</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1757,6 +2042,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>info@orbisdentalcare.com</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1770,13 +2060,18 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Orthodontist Tirana - Aurora Dental Clinic</t>
+          <t>Orthodontist Tirana</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1803,7 +2098,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Klinika Ortholux® është e vetmja klinikë në Shqipëri me ...</t>
+          <t>Klinika Ortholux® është e vetmja klinikë në Shqipëri me</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1830,7 +2125,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Teeth Whitening in Oxa Clinic in Tirana.</t>
+          <t>Oxa Clinic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1958,7 +2253,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EmdoDent | Expert Dental Care &amp; Implants in Tirana, Albania</t>
+          <t>EmdoDent</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1966,6 +2261,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>dent.emdo@gmail.com</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -1979,13 +2279,18 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dental care in Tirana, Albania</t>
+          <t>Dental care in Tirana</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2025,6 +2330,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>info@qanomed.com</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -2038,13 +2348,18 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DCA-Dental Center Albania Reviews 50</t>
+          <t>Dental Center Albania</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2052,6 +2367,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>info@dca.al</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -2065,13 +2385,18 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DCA - Dental Center Albania | Tirana</t>
+          <t>DCA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2098,7 +2423,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dental Center Albania Clinic - Compare Availability, Reviews ...</t>
+          <t>Dental Center Albania</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2106,6 +2431,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>info@dentaltourismalbania.com</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -2119,13 +2449,18 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:35</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>#holliwoodsmile #tirana #albania @dental_center_albania ...</t>
+          <t>#holliwoodsmile #tirana #albania @dental_center_albania</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2152,7 +2487,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dental Center Albania - Reviews, Photos &amp; Phone Number ...</t>
+          <t>Dental Center Albania</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2179,7 +2514,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oral Surgery Tirana, Albania - Art Dent Clinic</t>
+          <t>Oral Surgery Tirana</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2206,7 +2541,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ledismile – Dental &amp; Aesthetic Clinic in Albania</t>
+          <t>Ledismile</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2214,6 +2549,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>klinikaledismile@gmail.com</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -2227,13 +2567,18 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Orthognathic surgery - Tiranë</t>
+          <t>Salus Clinic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2246,6 +2591,11 @@
           <t>+355682053180</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>info@salus.al</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -2259,6 +2609,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:35</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2652,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Klinika Dentare KZP | Tirana - Facebook</t>
+          <t>Klinika Dentare KZP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2324,7 +2679,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dental Zone - Klinike Dentare | Tirana - Facebook</t>
+          <t>Dental Zone</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2351,7 +2706,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Klejdent-Klinike dentare | Tirana - Facebook</t>
+          <t>Klejdent-Klinike dentare</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2383,7 +2738,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dentalba - Klinikë Dentare Dhe Mjekësore | Tirana - Facebook</t>
+          <t>Dentalba</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2415,7 +2770,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Klinike Dentare Dr Blerina Kote | Tirana - Facebook</t>
+          <t>Klinike Dentare Dr Blerina Kote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2442,7 +2797,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Klinike Dentare "dental" | Tirana - Facebook</t>
+          <t>Klinike Dentare "dental"</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2469,7 +2824,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>32 Dental Klinike Dentare | Tirana - Facebook</t>
+          <t>32 Dental Klinike Dentare</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2501,7 +2856,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Klinike dentare 2A dent | Tirana - Facebook</t>
+          <t>Klinike dentare 2A dent</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2528,7 +2883,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ISmile Klinike Dentare | Tirana - Facebook</t>
+          <t>ISmile Klinike Dentare</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2560,7 +2915,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hair Transplant in Albania Tirana</t>
+          <t>Hair Solution Clinic</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2568,6 +2923,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>info@hairsolutionclinic.com</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -2581,13 +2941,18 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Hair transplant in Albania | Advanced Hair Clinic in Tirana</t>
+          <t>Advanced FUE Clinic</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2595,6 +2960,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>info@advancedfueclinic.com</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -2608,13 +2978,18 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Klinika Laser Way - Hair Transplant Center - Tirana</t>
+          <t>Klinika Laser Way</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2641,7 +3016,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nobi Hair Clinic: Hair transplant in Albania</t>
+          <t>Nobi Hair Clinic</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2668,7 +3043,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HAIR TRANSPLANT -TRAPIANTO CAPELLI ALBANIA ...</t>
+          <t>HAIR TRANSPLANT -TRAPIANTO CAPELLI ALBANIA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2700,7 +3075,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hair Transplant in Albania: Costs, Expert Clinics &amp; Guided ...</t>
+          <t>KEIT Clinic</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2731,13 +3106,18 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FUE Hair Transplant in Tirana</t>
+          <t>Istanbul Care</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2745,6 +3125,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>info@istanbul-care.com</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -2758,13 +3143,18 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>International Hair Clinic | Tirana</t>
+          <t>International Hair Clinic</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2823,7 +3213,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Leader Hair Transplantation Albania | Tirana</t>
+          <t>Leader Hair Transplantation Albania</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2850,7 +3240,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Hair Transplant Tirana with Micro FUE Technique</t>
+          <t>DaVinci Clinic</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2858,6 +3248,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>info@davinci.al</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -2871,13 +3266,18 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Hair Transplant in Albania - Affordable FUE &amp; DHI in Tirana</t>
+          <t>Estemoon Clinic</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2885,6 +3285,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>info@estemoon.com</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -2898,13 +3303,18 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kontakt - VatanMed | Klinike Mbjellje Flokesh Ne Tirane</t>
+          <t>VatanMed</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2935,13 +3345,18 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HAIR TRANSPLANT ALBANIA (@international_hair_clinic)</t>
+          <t>HAIR TRANSPLANT ALBANIA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2973,7 +3388,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MBJELLJE FLOKU me metoden FUE TIRANE: Tel:+355 4 ...</t>
+          <t>MBJELLJE FLOKU me metoden FUE TIRANE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3005,7 +3420,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dermolife Hair Clinic: Klinika e mbjelljes se Flokut ne Tirane</t>
+          <t>Dermolife Hair Clinic</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3036,13 +3451,18 @@
       <c r="G89" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>International Hair Clinic: Home</t>
+          <t>International Hair Clinic</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3050,6 +3470,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>info@internationalhairclinic.com</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -3063,13 +3488,18 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Best hair transplant clinic in Albania for natural results</t>
+          <t>Nouvelle Clinique</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3077,6 +3507,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>info@nouvelleclinique.com</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -3090,13 +3525,18 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mbjellje Floku &amp; Vetulla | Tirana - Facebook</t>
+          <t>Mbjellje Floku &amp; Vetulla</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3128,7 +3568,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Before and After Hair Transplant at Laser Way Clinic. Rezervo tani ...</t>
+          <t>Before and After Hair Transplant at Laser Way Clinic. Rezervo tani</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3182,7 +3622,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mbjellje floku me staf profesional dhe rezultate të sigurta ... - Facebook</t>
+          <t>Mbjellje floku me staf profesional dhe rezultate të sigurta</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3214,7 +3654,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Transplant flokesh në Klinikën Laser Way, zgjedhja e duhur për një ...</t>
+          <t>Transplant flokesh në Klinikën Laser Way, zgjedhja e duhur për një</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3241,7 +3681,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hair Transplant Center Rruga Ismail Qemali (ish Blloku ... - Facebook</t>
+          <t>Hair Transplant Center Rruga Ismail Qemali (ish Blloku</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3268,7 +3708,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KLINIKE PER MBJELLJE FLOKU – ADVANCED FUE CLINIC ...</t>
+          <t>Advanced FUE Clinic</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3276,6 +3716,11 @@
           <t>Tirana, Albania</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>info@advancedfueclinic.comadresa</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>HAIR_TRANSPLANT</t>
@@ -3289,13 +3734,18 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:36</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>vetëm te ADA Hair Clinic! Zgjidh metodën që të përshtatet: FUE, DHI ...</t>
+          <t>vetëm te ADA Hair Clinic! Zgjidh metodën që të përshtatet</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3322,7 +3772,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Riktheni flokët tuaj dhe rizbuloni veten me transplantin e flokëve në ...</t>
+          <t>Riktheni flokët tuaj dhe rizbuloni veten me transplantin e flokëve në</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3444,7 +3894,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VENTUS Dental Clinic - Klinike Dentare</t>
+          <t>VENTUS Dental Clinic</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3492,6 +3942,11 @@
           <t>069 512 2299</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>klinikaledismile@gmail.com</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -3510,11 +3965,16 @@
       <c r="H105" t="n">
         <v>8</v>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Daku Dental - Klinike Dentare - Implante Dentare</t>
+          <t>Daku Dental</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3549,7 +4009,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Empire Dental Clinic - Klinike Dentare</t>
+          <t>Empire Dental Clinic</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3560,6 +4020,11 @@
       <c r="C107" t="inlineStr">
         <is>
           <t>069 619 3302</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>info@empiredentalclinic.al</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3580,6 +4045,11 @@
       <c r="H107" t="n">
         <v>10</v>
       </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3614,7 +4084,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Klinika Dentare iDent - Dental Clinic</t>
+          <t>Klinika Dentare iDent</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3649,7 +4119,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Darvin Dental Clinic - Klinike Dentare</t>
+          <t>Darvin Dental Clinic</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3692,6 +4162,11 @@
           <t>069 319 1377</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>tiranadentalhospital@gmail.com</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -3710,6 +4185,11 @@
       <c r="H111" t="n">
         <v>10</v>
       </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3727,6 +4207,11 @@
           <t>068 806 6100</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>info@dca.al</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -3745,6 +4230,11 @@
       <c r="H112" t="n">
         <v>9</v>
       </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3832,6 +4322,11 @@
           <t>067 502 2333</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>info@dentalcareone.com</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -3850,6 +4345,11 @@
       <c r="H115" t="n">
         <v>10</v>
       </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3924,7 +4424,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Denti a Vita - Turismo Dentale - Dentisti in Albania</t>
+          <t>Denti a Vita</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3935,6 +4435,11 @@
       <c r="C118" t="inlineStr">
         <is>
           <t>+39 035 630 6649</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>info@dentiavita.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3955,11 +4460,16 @@
       <c r="H118" t="n">
         <v>9</v>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dental Tirana | Implantology &amp; Dental Aesthetics</t>
+          <t>Dental Tirana</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3970,6 +4480,11 @@
       <c r="C119" t="inlineStr">
         <is>
           <t>069 700 1002</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>dentaltirana8@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3990,11 +4505,16 @@
       <c r="H119" t="n">
         <v>10</v>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Implantus by Dr. Roland Zhuka - Dental Clinic in Tirana, Albania</t>
+          <t>Implantus by Dr. Roland Zhuka</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4005,6 +4525,11 @@
       <c r="C120" t="inlineStr">
         <is>
           <t>069 444 4016</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>info@implantus.al</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4025,11 +4550,16 @@
       <c r="H120" t="n">
         <v>10</v>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LELA DENTAL - Turismo dentale in Albania con clinica dentale e Dentisti a Tirana, cure per Denti e Sorrisi e impianti dentali</t>
+          <t>LELA DENTAL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4064,7 +4594,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dr. Roland Zhuka | Dentisti in Albania</t>
+          <t>Dr. Roland Zhuka</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4075,6 +4605,11 @@
       <c r="C122" t="inlineStr">
         <is>
           <t>069 704 4409</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>info@dr-rolandzhuka.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4095,6 +4630,11 @@
       <c r="H122" t="n">
         <v>10</v>
       </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4112,6 +4652,11 @@
           <t>069 777 0000</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>info@implant-house.al</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4130,11 +4675,16 @@
       <c r="H123" t="n">
         <v>7</v>
       </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Brianza Dent - Dental Day Hospital - Klinikë Dentare Prof. Dr. Luan Mavriqi</t>
+          <t>Brianza Dent</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4145,6 +4695,11 @@
       <c r="C124" t="inlineStr">
         <is>
           <t>068 203 2462</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>info@brianzadent.al</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4165,6 +4720,11 @@
       <c r="H124" t="n">
         <v>9</v>
       </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:38</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4182,6 +4742,11 @@
           <t>069 513 1451</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>info@klinikadentarelako.al</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4200,6 +4765,11 @@
       <c r="H125" t="n">
         <v>10</v>
       </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4217,6 +4787,11 @@
           <t>069 206 3230</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>info@website.com</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4235,11 +4810,16 @@
       <c r="H126" t="n">
         <v>10</v>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sorriso Sicuro Clinica Dentaria in Albania | Cure dentali in Albania</t>
+          <t>Sorriso Sicuro Clinica Dentaria in Albania</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4287,6 +4867,11 @@
           <t>069 608 9888</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>info@aicdent.al</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4305,11 +4890,16 @@
       <c r="H128" t="n">
         <v>8</v>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Vita Dent - Klinike Dentare &amp; Ortodontist Dr. Jonida Spaho</t>
+          <t>Vita Dent</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4352,6 +4942,11 @@
           <t>069 229 2506</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>orthosmiletirana@gmail.com</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4370,11 +4965,16 @@
       <c r="H130" t="n">
         <v>9</v>
       </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dr.Edlira Baruti Klinika Dentare Edlirdent - Ortodonti Tiranë - Drejtimi i dhëmbëve</t>
+          <t>Dr.Edlira Baruti Klinika Dentare Edlirdent</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4409,7 +5009,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Klinika OrthoLUX - Digital Orthodontic Clinic</t>
+          <t>Klinika OrthoLUX</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4420,6 +5020,11 @@
       <c r="C132" t="inlineStr">
         <is>
           <t>069 404 2956</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>klinikaortholux@gmail.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4440,6 +5045,11 @@
       <c r="H132" t="n">
         <v>10</v>
       </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4517,6 +5127,11 @@
           <t>069 340 3470</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>info@aidendental.al</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4535,11 +5150,16 @@
       <c r="H135" t="n">
         <v>10</v>
       </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:39</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>International Dental Clinic - Clinica Dentale Albania, Turismo Dentale</t>
+          <t>International Dental Clinic</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4550,6 +5170,11 @@
       <c r="C136" t="inlineStr">
         <is>
           <t>+39 329 463 0993</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>info@dentista-estero.net</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4570,6 +5195,11 @@
       <c r="H136" t="n">
         <v>10</v>
       </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:40</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4617,6 +5247,11 @@
           <t>04 234 9233</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>qsut@shendetesia.gov.al</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4635,6 +5270,11 @@
       <c r="H138" t="n">
         <v>8</v>
       </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:40</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4652,6 +5292,11 @@
           <t>067 208 1818</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>info@diamond-dental.al</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4670,6 +5315,11 @@
       <c r="H139" t="n">
         <v>9</v>
       </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:40</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4709,7 +5359,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>City Dental Clinic CDC - Dentisti in Albania</t>
+          <t>City Dental Clinic CDC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4720,6 +5370,11 @@
       <c r="C141" t="inlineStr">
         <is>
           <t>068 510 7070</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>info@cdc.com.al</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4740,6 +5395,11 @@
       <c r="H141" t="n">
         <v>9</v>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:40</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4757,6 +5417,11 @@
           <t>067 213 2705</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>info@vrionidental.com</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -4775,6 +5440,11 @@
       <c r="H142" t="n">
         <v>9</v>
       </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:40</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4814,7 +5484,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Platinum Dental Clinic - Dentisti in Albania</t>
+          <t>Platinum Dental Clinic</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4825,6 +5495,11 @@
       <c r="C144" t="inlineStr">
         <is>
           <t>069 601 0760</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>preventivo.dentalplatinum@gmail.com</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4845,6 +5520,11 @@
       <c r="H144" t="n">
         <v>9</v>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4884,7 +5564,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Smile Provider | Clinica dentale Albania | Dental Clinic Tirana</t>
+          <t>Smile Provider</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4895,6 +5575,11 @@
       <c r="C146" t="inlineStr">
         <is>
           <t>069 808 2222</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>info@smile-provider.com</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4915,6 +5600,11 @@
       <c r="H146" t="n">
         <v>9</v>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4949,7 +5639,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>International Hair Clinic - Hair Transplant - Eyebrow Transplant</t>
+          <t>International Hair Clinic</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4999,7 +5689,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LASER WAY CLINIC - Hair Transplant Center -</t>
+          <t>LASER WAY CLINIC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5049,7 +5739,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nobi Hair Clinic | Trapianto Capelli Albania | Hair Transplant Albania</t>
+          <t>Nobi Hair Clinic</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5074,7 +5764,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Trapianto Di Capelli | Albania Hair Clinic</t>
+          <t>Trapianto Di Capelli</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5099,7 +5789,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Major Clinic Albania - Hair Transplant</t>
+          <t>Major Clinic Albania</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5124,7 +5814,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Novel Hair Clinic - Trapianto Capelli Albania</t>
+          <t>Novel Hair Clinic</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5462,6 +6152,11 @@
           <t>+39 379 314 8604</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>info@dentialbania.com</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -5480,11 +6175,16 @@
       <c r="H166" t="n">
         <v>9</v>
       </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DaVINCI - Chirurgia Plastica Italiana</t>
+          <t>DaVINCI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5509,7 +6209,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Klinika Estetike Dermolife - Kirurgjia Italiane</t>
+          <t>Klinika Estetike Dermolife</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5534,7 +6234,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Art Smile Clinic - Klinikë Dentare</t>
+          <t>Art Smile Clinic</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5637,6 +6337,11 @@
           <t>069 332 2972</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>info@odontica.al</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -5655,6 +6360,11 @@
       <c r="H172" t="n">
         <v>10</v>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5814,7 +6524,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dental Tourism Albania - Dentale Albania</t>
+          <t>Dentale Albania</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5825,6 +6535,11 @@
       <c r="C178" t="inlineStr">
         <is>
           <t>+39 350 936 5488</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>info@dentale-albania.com</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5845,6 +6560,11 @@
       <c r="H178" t="n">
         <v>9</v>
       </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5879,7 +6599,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Art Dent Clinic &amp; Laborator - Dental Clinic, Dental Tourism, Clinica Dentale</t>
+          <t>Art Dent Clinic &amp; Laborator</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5914,7 +6634,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ClassDent - Dentista in Albania</t>
+          <t>ClassDent</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5925,6 +6645,11 @@
       <c r="C181" t="inlineStr">
         <is>
           <t>069 793 2159</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>info@classdentist.com</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5945,6 +6670,11 @@
       <c r="H181" t="n">
         <v>2</v>
       </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:41</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6032,6 +6762,11 @@
           <t>068 212 1813</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>unikdentalcenter@gmail.com</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -6050,11 +6785,16 @@
       <c r="H184" t="n">
         <v>7</v>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:42</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DENT ITALIA - Klinikë Dentare</t>
+          <t>DENT ITALIA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6065,6 +6805,11 @@
       <c r="C185" t="inlineStr">
         <is>
           <t>068 316 1231</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>dentitalia.info@gmail.com</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6085,6 +6830,11 @@
       <c r="H185" t="n">
         <v>7</v>
       </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:42</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6154,7 +6904,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Virtus Dental Center - Dentisti in Albania</t>
+          <t>Virtus Dental Center</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6165,6 +6915,11 @@
       <c r="C188" t="inlineStr">
         <is>
           <t>069 271 1166</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>info@virtus.al</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6185,6 +6940,11 @@
       <c r="H188" t="n">
         <v>7</v>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:42</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6224,7 +6984,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Zeus Dental Clinic - Dentisti in Albania</t>
+          <t>Zeus Dental Clinic</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6235,6 +6995,11 @@
       <c r="C190" t="inlineStr">
         <is>
           <t>069 401 0220</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>info@zeusdentalclinic.com</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6255,6 +7020,11 @@
       <c r="H190" t="n">
         <v>10</v>
       </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:42</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6372,6 +7142,11 @@
           <t>069 350 6500</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>info@theclinic.al</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -6390,6 +7165,11 @@
       <c r="H194" t="n">
         <v>10</v>
       </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:42</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6509,7 +7289,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Silur Clinic - Klinika Silur</t>
+          <t>Silur Clinic</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6534,7 +7314,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>New Hair Tirana - Trapianto Capelli Albania</t>
+          <t>New Hair Tirana</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6559,7 +7339,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Dermolife Hair Clinic | Trapianto di Capelli Albania</t>
+          <t>Dermolife Hair Clinic</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6824,7 +7604,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Klinike Dentare Durres - Eart Dent</t>
+          <t>Klinike Dentare Durres</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6835,6 +7615,11 @@
       <c r="C211" t="inlineStr">
         <is>
           <t>069 797 8700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>eartdent222@gmail.com</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6855,11 +7640,16 @@
       <c r="H211" t="n">
         <v>2</v>
       </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Emerald Dental | Dentista Albania: Dal Volo alla Cura per Denti e Sorrisi</t>
+          <t>Emerald Dental</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6870,6 +7660,11 @@
       <c r="C212" t="inlineStr">
         <is>
           <t>069 205 7277</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>poliklinikaemerald@gmail.com</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6890,6 +7685,11 @@
       <c r="H212" t="n">
         <v>8</v>
       </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6924,7 +7724,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CityDent - Klinikë Dentare</t>
+          <t>CityDent</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6959,7 +7759,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Klinika Dentare Evidental — Dental Clinic</t>
+          <t>Klinika Dentare Evidental</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7209,7 +8009,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Dentisti in Albania - Trio Dental Center</t>
+          <t>Trio Dental Center</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7220,6 +8020,11 @@
       <c r="C223" t="inlineStr">
         <is>
           <t>069 747 4695</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>info@dentaltrio.com</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7240,6 +8045,11 @@
       <c r="H223" t="n">
         <v>7</v>
       </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7279,7 +8089,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Klinika DENTALB - Dental clinic in Tirana ,Albania</t>
+          <t>Klinika DENTALB</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7309,7 +8119,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Impianti Dentali Albania - Dentisti in Albania - Oxa Clinic</t>
+          <t>Oxa Clinic</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7320,6 +8130,11 @@
       <c r="C226" t="inlineStr">
         <is>
           <t>067 640 4805</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>info@oxaclinic.com</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7340,6 +8155,11 @@
       <c r="H226" t="n">
         <v>8</v>
       </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7432,6 +8252,11 @@
           <t>069 206 2408</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>albaniainfo@kissdent.infocall</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -7450,6 +8275,11 @@
       <c r="H230" t="n">
         <v>10</v>
       </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7529,7 +8359,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BlueMagic Group Clinic | Hair Transplant &amp; Dental Experts in Turkey</t>
+          <t>BlueMagic Group Clinic</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7604,7 +8434,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Family Dental Care: Turismo Dentale &amp; Dentisti in Albania</t>
+          <t>Family Dental Care</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7615,6 +8445,11 @@
       <c r="C237" t="inlineStr">
         <is>
           <t>069 704 3335</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>info@familydentalcareal.com</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -7635,6 +8470,11 @@
       <c r="H237" t="n">
         <v>9</v>
       </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:43</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7652,6 +8492,11 @@
           <t>069 577 7887</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>info@newsmile.al</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -7670,6 +8515,11 @@
       <c r="H238" t="n">
         <v>10</v>
       </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7709,7 +8559,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Klinika Dentare Toti &amp; Gurakuqi (Toti &amp; Gurakuqi Dental Clinic)</t>
+          <t>Klinika Dentare Toti &amp; Gurakuqi</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7720,6 +8570,11 @@
       <c r="C240" t="inlineStr">
         <is>
           <t>04 225 8429</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>info@toti-gurakuqi.al</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -7740,6 +8595,11 @@
       <c r="H240" t="n">
         <v>9</v>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7869,7 +8729,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Dental Clinic - Dentist in Albania - Smart Dent - Klinike Dentare</t>
+          <t>Smart Dental Clinic</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7904,7 +8764,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>B.E.L. Dent - Dentist, Dentista in Albania, Klinike dentare, Dentist near me, Cosmetic dentist, Dentist office, Zahnartz</t>
+          <t>B.E.L. Dent</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7915,6 +8775,11 @@
       <c r="C246" t="inlineStr">
         <is>
           <t>068 282 0771</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>b.e.l.dentclinic@gmail.com</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -7935,11 +8800,16 @@
       <c r="H246" t="n">
         <v>10</v>
       </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Klinika Dentare Sident - Dental care Center</t>
+          <t>Klinika Dentare Sident</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8077,6 +8947,11 @@
           <t>068 514 4440</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>klinikadentarevraja@yahoo.com</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -8095,6 +8970,11 @@
       <c r="H251" t="n">
         <v>5</v>
       </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8362,6 +9242,11 @@
           <t>068 209 2077</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>info@lineadental.al</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -8380,6 +9265,11 @@
       <c r="H260" t="n">
         <v>8</v>
       </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8637,6 +9527,11 @@
           <t>068 402 2853</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>web@dentalnobel.com</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -8655,6 +9550,11 @@
       <c r="H269" t="n">
         <v>10</v>
       </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:44</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8724,7 +9624,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Dental Care - Klinika Dentare "Dental Care" - Klinike Dentare Durres</t>
+          <t>Dental Care</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8884,7 +9784,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Max Dent - Klinikë dentare, Dental Clinic in Albania, Dental Tourism Albania</t>
+          <t>Max Dent</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8949,7 +9849,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Klinika Dentare Prodent - Dr. Linda Saraçi Mehmetaj</t>
+          <t>Klinika Dentare Prodent</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8979,7 +9879,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Klinika Dentare - Mat Dental</t>
+          <t>Mat Dental</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8990,6 +9890,11 @@
       <c r="C280" t="inlineStr">
         <is>
           <t>069 445 7000</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>info@matdental.com</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9010,6 +9915,11 @@
       <c r="H280" t="n">
         <v>10</v>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9109,7 +10019,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Klinika Dentare A. Shabani - Durres, Albania</t>
+          <t>Klinika Dentare A. Shabani</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9120,6 +10030,11 @@
       <c r="C284" t="inlineStr">
         <is>
           <t>069 587 5913</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>contatto@esempio.it</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9140,6 +10055,11 @@
       <c r="H284" t="n">
         <v>2</v>
       </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9187,6 +10107,11 @@
           <t>069 317 7957</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>info@drteeth.al</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -9205,6 +10130,11 @@
       <c r="H286" t="n">
         <v>9</v>
       </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9239,7 +10169,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MasterDent - Dental Clinic</t>
+          <t>MasterDent</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9250,6 +10180,11 @@
       <c r="C288" t="inlineStr">
         <is>
           <t>069 923 2323</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>info@masterdent.al</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9270,6 +10205,11 @@
       <c r="H288" t="n">
         <v>9</v>
       </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9299,7 +10239,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DentAurum - Klinikë Dentare</t>
+          <t>DentAurum</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9310,6 +10250,11 @@
       <c r="C290" t="inlineStr">
         <is>
           <t>069 784 1479</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>dent.aurum.al@gmail.com</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9330,6 +10275,11 @@
       <c r="H290" t="n">
         <v>10</v>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9659,7 +10609,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Ikera Dent - Klinike Dentare</t>
+          <t>Ikera Dent</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9702,6 +10652,11 @@
           <t>069 477 8770</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>mezinident@gmail.com</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -9720,6 +10675,11 @@
       <c r="H303" t="n">
         <v>7</v>
       </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9732,6 +10692,11 @@
           <t>Reuga Metush Luli Prane Tregut Te shkolles bashkume Apartament ne zonen kadastrale 8120, nr pasurie 7/239 1-2, Tiranë</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>info@inalbania.al</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -9750,6 +10715,11 @@
       <c r="H304" t="n">
         <v>8</v>
       </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9797,6 +10767,11 @@
           <t>067 205 7461</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>info@manjanidental.com</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -9815,6 +10790,11 @@
       <c r="H306" t="n">
         <v>9</v>
       </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10009,7 +10989,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Klinike Dentare Durres - Royal Crown</t>
+          <t>Klinike Dentare Durres</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10227,6 +11207,11 @@
           <t>068 868 1632</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>info@albest.al</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -10245,6 +11230,11 @@
       <c r="H320" t="n">
         <v>9</v>
       </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10279,7 +11269,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Tani Dent - Klinike Dentare dhe Laborator</t>
+          <t>Tani Dent</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10339,7 +11329,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>DRV Clinic Albania (Klinike Dentare &amp; Estetike Italo-Angleze)</t>
+          <t>DRV Clinic Albania</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10417,6 +11407,11 @@
           <t>068 200 0620</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>info@mariusidentalclinic.com</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -10435,6 +11430,11 @@
       <c r="H326" t="n">
         <v>5</v>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10614,7 +11614,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CreaDent | Dental Clinic and Lab in Tirana</t>
+          <t>CreaDent</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10625,6 +11625,11 @@
       <c r="C333" t="inlineStr">
         <is>
           <t>067 208 2992</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>info@creadent.al</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -10645,6 +11650,11 @@
       <c r="H333" t="n">
         <v>9</v>
       </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:46</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -10662,6 +11672,11 @@
           <t>069 407 0666</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>klinika@albdental.com</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -10680,6 +11695,11 @@
       <c r="H334" t="n">
         <v>2</v>
       </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11122,6 +12142,11 @@
           <t>069 505 0111</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>info@endetadentalclinic.al</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11140,6 +12165,11 @@
       <c r="H349" t="n">
         <v>6</v>
       </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11239,7 +12269,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Odonto Derma | Klinikë Dentare &amp; Estetike</t>
+          <t>Odonto Derma</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -11317,6 +12347,11 @@
           <t>069 205 3494</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>premiumdentalcare2024@gmail.com</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11335,11 +12370,16 @@
       <c r="H355" t="n">
         <v>9</v>
       </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Avante Dental Clinic Durres - Veneers, Implants &amp; Smile Design Albania</t>
+          <t>Avante Dental Clinic Durres</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11369,7 +12409,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Dentisti in Albania - Andent Clinic</t>
+          <t>Andent Clinic</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11404,7 +12444,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Radiance Dental Hospital - Turismo Dentale in Albania</t>
+          <t>Radiance Dental Hospital</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11415,6 +12455,11 @@
       <c r="C358" t="inlineStr">
         <is>
           <t>068 668 8888</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>info@radiance.al</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -11435,6 +12480,11 @@
       <c r="H358" t="n">
         <v>10</v>
       </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11452,6 +12502,11 @@
           <t>069 604 5701</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>info@mail.com</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11470,11 +12525,16 @@
       <c r="H359" t="n">
         <v>8</v>
       </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Clinica del Sorriso Tirana - Turismo Dentale in Albania</t>
+          <t>Clinica del Sorriso Tirana</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11485,6 +12545,11 @@
       <c r="C360" t="inlineStr">
         <is>
           <t>069 581 7212</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>info@cstdentalclinic.it</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11505,11 +12570,16 @@
       <c r="H360" t="n">
         <v>9</v>
       </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Juar Dent - Klinike Dentare</t>
+          <t>Juar Dent</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11539,7 +12609,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Dentisti in Albania - Clinica Dentale a Tirana - Impianti Dentali - Ortodonzia - Turismo Dentale - Ayna Dental Clinic</t>
+          <t>Clinica Dentale a Tirana</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11609,7 +12679,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Clinica Dentale Durazzo - Dentital: Turismo dentale in Albania. Prezzi low cost. Dentista</t>
+          <t>Clinica Dentale Durazzo</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11692,6 +12762,11 @@
           <t>067 212 5979</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>klinike.laura.dent@gmail.com</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11710,11 +12785,16 @@
       <c r="H366" t="n">
         <v>9</v>
       </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:48</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ami Dental - Dental Clinic in Durrës</t>
+          <t>Ami Dental</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11725,6 +12805,11 @@
       <c r="C367" t="inlineStr">
         <is>
           <t>069 559 9899</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>amidentaldurres@gmail.com</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -11745,6 +12830,11 @@
       <c r="H367" t="n">
         <v>2</v>
       </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:48</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -11762,6 +12852,11 @@
           <t>069 208 8948</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>danielkurti1982@gmail.com</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11780,6 +12875,11 @@
       <c r="H368" t="n">
         <v>2</v>
       </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:48</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -11797,6 +12897,11 @@
           <t>069 350 4123</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>info@surrideodentalcare.com</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11815,11 +12920,16 @@
       <c r="H369" t="n">
         <v>2</v>
       </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:48</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Klinike Dentare - ISUFI ROYAL DENTAL</t>
+          <t>ISUFI ROYAL DENTAL</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11867,6 +12977,11 @@
           <t>067 202 2294</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>tuoindirizzo@email.com</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11885,11 +13000,16 @@
       <c r="H371" t="n">
         <v>10</v>
       </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:48</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Klinika VitalDent – Dr. Juliana Tara ER</t>
+          <t>Klinika VitalDent</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11900,6 +13020,11 @@
       <c r="C372" t="inlineStr">
         <is>
           <t>067 259 7018</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>info@vitaldent.com</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -11920,6 +13045,11 @@
       <c r="H372" t="n">
         <v>10</v>
       </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -11937,6 +13067,11 @@
           <t>069 700 3003</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>info@ertaxhanari.com</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -11955,6 +13090,11 @@
       <c r="H373" t="n">
         <v>9</v>
       </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -11994,7 +13134,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>BLERINA DENT Vollga - Dr. Blerina Bani Topra - Dentist Durres ,Albania Pro Implants &amp; Aesthetic Dentistry</t>
+          <t>BLERINA DENT Vollga</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -12042,6 +13182,11 @@
           <t>069 669 9944</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>info@florentiadent.com</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -12060,6 +13205,11 @@
       <c r="H376" t="n">
         <v>9</v>
       </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12099,7 +13249,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Emma Dental Center - Impianti Dentali in Albania</t>
+          <t>Emma Dental Center</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -12147,6 +13297,11 @@
           <t>069 582 3182</t>
         </is>
       </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>studio@sorrisodental.al</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -12165,6 +13320,11 @@
       <c r="H379" t="n">
         <v>8</v>
       </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12322,6 +13482,11 @@
           <t>067 206 6800</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>info@dental-estetik.al</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -12340,11 +13505,16 @@
       <c r="H384" t="n">
         <v>9</v>
       </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Confident Dental Clinic - Klinike dentare</t>
+          <t>Confident Dental Clinic</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -12444,7 +13614,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Turismo Dentale in Albania: Dent Dinamo AL</t>
+          <t>Dent Dinamo</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -12455,6 +13625,11 @@
       <c r="C388" t="inlineStr">
         <is>
           <t>069 228 4409</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>info@dentdinamo.com</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -12475,6 +13650,11 @@
       <c r="H388" t="n">
         <v>10</v>
       </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12632,6 +13812,11 @@
           <t>04 225 1944</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>info@dodbibadental.al</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -12650,6 +13835,11 @@
       <c r="H393" t="n">
         <v>10</v>
       </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -12954,7 +14144,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Dentisti in Albania - Turismo Dentale - Studio Dentale - Prezzi Bassi - Clinica Dentale Luna</t>
+          <t>Turismo Dentale</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12989,7 +14179,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Turismo Dentale in Albania, Dentisti Albania - Dental Care Albania</t>
+          <t>Dental Care Albania</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -13000,6 +14190,11 @@
       <c r="C404" t="inlineStr">
         <is>
           <t>069 218 6868</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>info@dentalcarealbania.com</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13020,6 +14215,11 @@
       <c r="H404" t="n">
         <v>8</v>
       </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13089,7 +14289,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>DR.BENARDA BEQARAJ - MJEKE STOMATOLOGE -DENTISTE</t>
+          <t>Dr. Benarda Beqaraj</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -13100,6 +14300,11 @@
       <c r="C407" t="inlineStr">
         <is>
           <t>067 613 1738</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>info@benarda.com</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -13120,11 +14325,16 @@
       <c r="H407" t="n">
         <v>9</v>
       </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Turismo Dentale Albania a Tirana</t>
+          <t>Marco Licata Dental</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13135,6 +14345,11 @@
       <c r="C408" t="inlineStr">
         <is>
           <t>+39 391 314 4477</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>marcolicata69@gmail.com</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13155,6 +14370,11 @@
       <c r="H408" t="n">
         <v>10</v>
       </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13224,7 +14444,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>OÇO Dental Clinic in Tirana, Albania</t>
+          <t>OÇO Dental Clinic in Tirana</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13235,6 +14455,11 @@
       <c r="C411" t="inlineStr">
         <is>
           <t>067 204 0100</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>hi@beacon.io</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13255,6 +14480,11 @@
       <c r="H411" t="n">
         <v>10</v>
       </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -13289,7 +14519,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Elda Dent - Klinike Dentare</t>
+          <t>Elda Dent</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -13337,6 +14567,11 @@
           <t>069 484 0698</t>
         </is>
       </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>info@deltadentacademy.com</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -13355,6 +14590,11 @@
       <c r="H414" t="n">
         <v>9</v>
       </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:50</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -13429,7 +14669,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fida dental &amp; lab - Dentisti in Albania</t>
+          <t>Fida dental &amp; lab</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -13649,7 +14889,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Studio Dentare - Eno Gaçe (Dentist për Fëmijë)</t>
+          <t>Studio Dentare</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13869,7 +15109,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Studio Doctor Smile - Tirane</t>
+          <t>Studio Doctor Smile</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13959,7 +15199,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Dental &amp; Beauty | Chirurgia estetica | Impianti dentali</t>
+          <t>Dental &amp; Beauty</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -13970,6 +15210,11 @@
       <c r="C434" t="inlineStr">
         <is>
           <t>069 585 0555</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>info@dentalandbeauty.it</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -13990,6 +15235,11 @@
       <c r="H434" t="n">
         <v>9</v>
       </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:51</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -14327,6 +15577,11 @@
           <t>069 213 2411</t>
         </is>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>ikaraj93@gmail.com</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -14345,6 +15600,11 @@
       <c r="H445" t="n">
         <v>2</v>
       </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:51</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -14409,7 +15669,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Klinika Dentare - AzDental</t>
+          <t>AzDental</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -14544,7 +15804,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Smiles of Aida - Dental Clinic</t>
+          <t>Smiles of Aida</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -14717,6 +15977,11 @@
           <t>067 208 0977</t>
         </is>
       </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>info@amadentistry.com</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -14735,6 +16000,11 @@
       <c r="H457" t="n">
         <v>10</v>
       </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:51</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -14944,7 +16214,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>DENTALVITA ALBANIA | TURISMO DENTALE</t>
+          <t>DENTALVITA ALBANIA</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -14955,6 +16225,11 @@
       <c r="C465" t="inlineStr">
         <is>
           <t>+39 388 428 4873</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>dentalvitaturismodentale@gmail.com</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -14975,6 +16250,11 @@
       <c r="H465" t="n">
         <v>1</v>
       </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:51</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -14992,6 +16272,11 @@
           <t>+39 0141 180 8901</t>
         </is>
       </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>info@mysite.com</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -15010,6 +16295,11 @@
       <c r="H466" t="n">
         <v>9</v>
       </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:51</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -15099,7 +16389,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Massimo Sopranzi</t>
+          <t>Massimo Sopranzi Dental</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -15110,6 +16400,11 @@
       <c r="C470" t="inlineStr">
         <is>
           <t>+39 333 830 9081</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>metodosopranzi@gmail.com</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -15130,6 +16425,11 @@
       <c r="H470" t="n">
         <v>10</v>
       </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -15199,7 +16499,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Family Dental - Clinica Dentale in Albania (Fier)</t>
+          <t>Family Dental</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -15210,6 +16510,11 @@
       <c r="C473" t="inlineStr">
         <is>
           <t>069 366 9726</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>info@family-dental.it</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -15230,6 +16535,11 @@
       <c r="H473" t="n">
         <v>1</v>
       </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -15399,7 +16709,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Dentisti in Albania - Dental Care Albania</t>
+          <t>Dental Care Albania</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -15410,6 +16720,11 @@
       <c r="C479" t="inlineStr">
         <is>
           <t>069 218 6868</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>info@dentalcarealbania.com</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -15430,6 +16745,11 @@
       <c r="H479" t="n">
         <v>1</v>
       </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -15469,7 +16789,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Grafi dhëmbësh - Panoramex dixhital</t>
+          <t>Grafi dhëmbësh</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -15559,7 +16879,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Dental clinic in Tirana | Dentist in Albania</t>
+          <t>Dental Clinic Tirana</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -15619,7 +16939,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>TURISTA SORRIDENTE</t>
+          <t>Turista Sorridente</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -15630,6 +16950,11 @@
       <c r="C486" t="inlineStr">
         <is>
           <t>069 461 1192</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>info@turistasorridente.it</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -15650,6 +16975,11 @@
       <c r="H486" t="n">
         <v>8</v>
       </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -15697,6 +17027,11 @@
           <t>069 206 0081</t>
         </is>
       </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>info@klejdent.com</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -15715,6 +17050,11 @@
       <c r="H488" t="n">
         <v>9</v>
       </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -15792,6 +17132,11 @@
           <t>069 606 6264</t>
         </is>
       </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>info@hygeiadent.com</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -15810,6 +17155,11 @@
       <c r="H491" t="n">
         <v>7</v>
       </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -15827,6 +17177,11 @@
           <t>068 665 8888</t>
         </is>
       </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>info@dentalhealth.al</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -15845,6 +17200,11 @@
       <c r="H492" t="n">
         <v>9</v>
       </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -15884,7 +17244,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Finesa Dental Clinic | Dentisti in Albania | Aesthetic Dentist | Klinike Dentare ne Tirane</t>
+          <t>Finesa Dental Clinic</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15895,6 +17255,11 @@
       <c r="C494" t="inlineStr">
         <is>
           <t>069 528 8188</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>info@finesadental.com</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -15915,6 +17280,11 @@
       <c r="H494" t="n">
         <v>8</v>
       </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -15967,6 +17337,11 @@
           <t>067 727 5136</t>
         </is>
       </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>adctirana@gmail.com</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -15985,6 +17360,11 @@
       <c r="H496" t="n">
         <v>8</v>
       </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -16072,6 +17452,11 @@
           <t>068 820 1762</t>
         </is>
       </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>info@tarjadentalclinic.com</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16090,6 +17475,11 @@
       <c r="H499" t="n">
         <v>2</v>
       </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -16167,6 +17557,11 @@
           <t>069 813 4463</t>
         </is>
       </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>info@dentists.al</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16185,6 +17580,11 @@
       <c r="H502" t="n">
         <v>7</v>
       </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -16232,6 +17632,11 @@
           <t>069 202 6898</t>
         </is>
       </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>celamiaurora@gmail.com</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16250,6 +17655,11 @@
       <c r="H504" t="n">
         <v>2</v>
       </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -16332,6 +17742,11 @@
           <t>069 625 1111</t>
         </is>
       </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>info@medicaltourisminalbania.com</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16350,6 +17765,11 @@
       <c r="H507" t="n">
         <v>10</v>
       </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -16432,6 +17852,11 @@
           <t>068 200 4418</t>
         </is>
       </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>info@albmedtour.it</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16450,6 +17875,11 @@
       <c r="H510" t="n">
         <v>7</v>
       </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -16467,6 +17897,11 @@
           <t>069 224 9288</t>
         </is>
       </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>info@dentisti-albania.it</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16485,6 +17920,11 @@
       <c r="H511" t="n">
         <v>10</v>
       </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -16502,6 +17942,11 @@
           <t>069 401 0700</t>
         </is>
       </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>info@dentadent.al</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16520,6 +17965,11 @@
       <c r="H512" t="n">
         <v>9</v>
       </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -16659,7 +18109,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Dental Clinic in Tirana - Queen Dental</t>
+          <t>Queen Dental</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -16670,6 +18120,11 @@
       <c r="C517" t="inlineStr">
         <is>
           <t>069 602 0066</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>example@mail.com</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -16690,11 +18145,16 @@
       <c r="H517" t="n">
         <v>9</v>
       </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:54</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Dental Tours - Dental implants clinic in Albania</t>
+          <t>Dental Tours</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -16742,6 +18202,11 @@
           <t>069 878 4104</t>
         </is>
       </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2mdentalcliniclab@gmail.com</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16760,6 +18225,11 @@
       <c r="H519" t="n">
         <v>9</v>
       </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -16799,7 +18269,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>San Marco Dental, Dentisti in Albania, Turismo Dentale</t>
+          <t>San Marco Dental</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -16810,6 +18280,11 @@
       <c r="C521" t="inlineStr">
         <is>
           <t>069 700 7770</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>info@sanmarcodental.com</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -16830,6 +18305,11 @@
       <c r="H521" t="n">
         <v>8</v>
       </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -16869,7 +18349,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Clinica Bright Pro Dental - Dentisti in Albania</t>
+          <t>Clinica Bright Pro Dental</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -16947,6 +18427,11 @@
           <t>068 332 6375</t>
         </is>
       </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>dreamdentaltirana@gmail.com</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -16965,6 +18450,11 @@
       <c r="H525" t="n">
         <v>9</v>
       </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -17102,6 +18592,11 @@
           <t>068 200 7447</t>
         </is>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>info@travelandsmile.co.uk</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17120,6 +18615,11 @@
       <c r="H530" t="n">
         <v>10</v>
       </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -17219,7 +18719,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>KDC - Kosiqi Dental Clinic</t>
+          <t>KDC</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17384,7 +18884,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Dentisti in Albania | Turismo Dentale | Clinius Dental Center</t>
+          <t>Turismo Dentale</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17432,6 +18932,11 @@
           <t>069 343 3300</t>
         </is>
       </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>contact@mbtdentalpro.com</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17450,6 +18955,11 @@
       <c r="H540" t="n">
         <v>10</v>
       </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -17467,6 +18977,11 @@
           <t>069 205 0512</t>
         </is>
       </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>info@test.com</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17485,6 +19000,11 @@
       <c r="H541" t="n">
         <v>2</v>
       </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:55</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -17567,6 +19087,11 @@
           <t>069 555 1566</t>
         </is>
       </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>info@ajnadental.al</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17585,6 +19110,11 @@
       <c r="H544" t="n">
         <v>7</v>
       </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:56</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -17627,6 +19157,11 @@
           <t>068 400 9191</t>
         </is>
       </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>info@aldental.al</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17645,11 +19180,16 @@
       <c r="H546" t="n">
         <v>9</v>
       </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:56</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Ritorna A Sorridere - By Shehu Dental Clinic</t>
+          <t>Ritorna A Sorridere</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17697,6 +19237,11 @@
           <t>069 674 8119</t>
         </is>
       </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>info@dalux.al</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17715,6 +19260,11 @@
       <c r="H548" t="n">
         <v>8</v>
       </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:56</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -17767,6 +19317,11 @@
           <t>069 339 8188</t>
         </is>
       </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>info@ambeldentalclinic.al</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17785,6 +19340,11 @@
       <c r="H550" t="n">
         <v>9</v>
       </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:56</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -17802,6 +19362,11 @@
           <t>069 322 2230</t>
         </is>
       </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>info@sulajdentalclinic.com</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -17820,6 +19385,11 @@
       <c r="H551" t="n">
         <v>8</v>
       </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:56</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -18044,7 +19614,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Dential - Clinica Dentale Odontoiatrica</t>
+          <t>Dential</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18055,6 +19625,11 @@
       <c r="C559" t="inlineStr">
         <is>
           <t>+39 331 130 1957</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>info@dential.net</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -18075,6 +19650,11 @@
       <c r="H559" t="n">
         <v>2</v>
       </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:57</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -18242,6 +19822,11 @@
           <t>069 570 7141</t>
         </is>
       </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>contact@trusmile.com</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr">
         <is>
           <t>DENTAL</t>
@@ -18260,6 +19845,11 @@
       <c r="H565" t="n">
         <v>9</v>
       </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:57</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -18409,7 +19999,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Dental Tourism Albania - Dental Clinic Albania</t>
+          <t>Dental Care Albania</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18420,6 +20010,11 @@
       <c r="C571" t="inlineStr">
         <is>
           <t>069 218 6868</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>info@dentalcarealbania.com</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -18440,6 +20035,11 @@
       <c r="H571" t="n">
         <v>10</v>
       </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:57</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -18999,7 +20599,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>WeSmile Albania - Dental Clinic - Assoc.Prof. Dorjan Hysi</t>
+          <t>WeSmile Albania</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -19309,7 +20909,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Professional Dental Clinic - Dr. Iris Kallmi (Shkëmbi)</t>
+          <t>Professional Dental Clinic</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -19444,7 +21044,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Trapianto Di Capelli | Capelli Albania Clinic</t>
+          <t>Trapianto Di Capelli</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -19469,7 +21069,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>IstCare Clinic Tirana, Albania</t>
+          <t>IstCare Clinic Tirana</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -19494,7 +21094,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>ESTEMOON | Hair Transplant in Albania</t>
+          <t>ESTEMOON</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
